--- a/Inputs/EQR_data_for_comparison.xlsx
+++ b/Inputs/EQR_data_for_comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gamtostyrimai-my.sharepoint.com/personal/nathan_baker_gamtc_lt/Documents/MOBILR Project (2024-2027)/Analyses/Operational taxalist/Calculating OTL indices/Inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="13_ncr:1_{084EDBE5-1F93-4313-A408-BFB5CB6B0B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E4DACE4-8C99-450E-BE47-8EEEA390A83F}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="13_ncr:1_{084EDBE5-1F93-4313-A408-BFB5CB6B0B16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{152F2FC2-2F3A-4E2D-9766-1447F2AC2C48}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{8496B6AF-7CC8-4469-A242-20E08F425910}"/>
+    <workbookView xWindow="38290" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{8496B6AF-7CC8-4469-A242-20E08F425910}"/>
   </bookViews>
   <sheets>
     <sheet name="Lapas2" sheetId="2" r:id="rId1"/>
@@ -1199,31 +1199,31 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="D2" s="9">
         <v>1</v>
       </c>
-      <c r="E2" s="18">
-        <v>54.879600000000003</v>
-      </c>
-      <c r="F2" s="18">
-        <v>22.993400000000001</v>
-      </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="13" t="s">
-        <v>17</v>
+      <c r="E2" s="19">
+        <v>55.842799999999997</v>
+      </c>
+      <c r="F2" s="19">
+        <v>23.886399999999998</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>60</v>
       </c>
       <c r="I2" s="9">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2" s="9">
         <v>10</v>
@@ -1232,1198 +1232,1198 @@
         <v>2021</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="M2" s="10">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="N2" s="10" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="17">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="D3" s="9">
         <v>1</v>
       </c>
-      <c r="E3" s="18">
-        <v>54.879600000000003</v>
-      </c>
-      <c r="F3" s="18">
-        <v>22.993400000000001</v>
-      </c>
-      <c r="G3" t="s">
-        <v>16</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>20</v>
+      <c r="E3" s="19">
+        <v>55.266034769999997</v>
+      </c>
+      <c r="F3" s="19">
+        <v>21.454944709999999</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="I3" s="9">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J3" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" s="9">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="M3" s="10">
-        <v>0.36</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="N3" s="10" t="s">
-        <v>19</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="17">
-        <v>65</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="9">
         <v>1</v>
       </c>
       <c r="E4" s="18">
-        <v>55.420122130000003</v>
+        <v>55.780200000000001</v>
       </c>
       <c r="F4" s="18">
-        <v>25.10494164</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="6">
-        <v>18</v>
-      </c>
-      <c r="J4" s="6">
+        <v>21.2561</v>
+      </c>
+      <c r="G4" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="I4" s="9">
+        <v>21</v>
+      </c>
+      <c r="J4" s="9">
         <v>9</v>
       </c>
-      <c r="K4" s="6">
-        <v>2019</v>
+      <c r="K4" s="9">
+        <v>2021</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0.76</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>26</v>
+        <v>74</v>
+      </c>
+      <c r="M4" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="17">
-        <v>80</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="5">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="9">
+        <v>4</v>
       </c>
       <c r="E5" s="18">
-        <v>55.420122130000003</v>
+        <v>55.2913</v>
       </c>
       <c r="F5" s="18">
-        <v>25.10494164</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="6">
+        <v>21.377199999999998</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="9">
+        <v>12</v>
+      </c>
+      <c r="J5" s="9">
+        <v>10</v>
+      </c>
+      <c r="K5" s="9">
+        <v>2015</v>
+      </c>
+      <c r="L5" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="M5" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="N5" s="10" t="s">
         <v>19</v>
-      </c>
-      <c r="J5" s="6">
-        <v>9</v>
-      </c>
-      <c r="K5" s="6">
-        <v>2022</v>
-      </c>
-      <c r="L5" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0.99</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="17">
-        <v>81</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="9">
         <v>1</v>
       </c>
       <c r="E6" s="18">
-        <v>55.420122130000003</v>
+        <v>54.879600000000003</v>
       </c>
       <c r="F6" s="18">
-        <v>25.10494164</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="6">
-        <v>20</v>
-      </c>
-      <c r="J6" s="6">
-        <v>9</v>
-      </c>
-      <c r="K6" s="6">
-        <v>2016</v>
+        <v>22.993400000000001</v>
+      </c>
+      <c r="G6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="9">
+        <v>7</v>
+      </c>
+      <c r="J6" s="9">
+        <v>10</v>
+      </c>
+      <c r="K6" s="9">
+        <v>2021</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="M6" s="7">
-        <v>1</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>29</v>
+        <v>18</v>
+      </c>
+      <c r="M6" s="10">
+        <v>0.35</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="17">
-        <v>60</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="9">
         <v>1</v>
       </c>
       <c r="E7" s="18">
-        <v>54.755461689999997</v>
+        <v>54.879600000000003</v>
       </c>
       <c r="F7" s="18">
-        <v>24.957577279999999</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="6">
-        <v>30</v>
-      </c>
-      <c r="J7" s="6">
-        <v>9</v>
-      </c>
-      <c r="K7" s="6">
-        <v>2019</v>
+        <v>22.993400000000001</v>
+      </c>
+      <c r="G7" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="9">
+        <v>2</v>
+      </c>
+      <c r="J7" s="9">
+        <v>10</v>
+      </c>
+      <c r="K7" s="9">
+        <v>2017</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="7">
-        <v>0.73</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>26</v>
+        <v>21</v>
+      </c>
+      <c r="M7" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="17">
-        <v>63</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="9">
         <v>1</v>
       </c>
       <c r="E8" s="18">
-        <v>54.755461689999997</v>
+        <v>55.780200000000001</v>
       </c>
       <c r="F8" s="18">
-        <v>24.957577279999999</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="6">
-        <v>26</v>
-      </c>
-      <c r="J8" s="6">
+        <v>21.2561</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="I8" s="9">
+        <v>18</v>
+      </c>
+      <c r="J8" s="9">
         <v>9</v>
       </c>
-      <c r="K8" s="6">
-        <v>2022</v>
+      <c r="K8" s="9">
+        <v>2018</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0.75</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>26</v>
+        <v>76</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="17">
-        <v>71</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="5">
-        <v>1</v>
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="9">
+        <v>3</v>
       </c>
       <c r="E9" s="18">
-        <v>54.755461689999997</v>
+        <v>55.479500000000002</v>
       </c>
       <c r="F9" s="18">
-        <v>24.957577279999999</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="6">
-        <v>28</v>
-      </c>
-      <c r="J9" s="6">
+        <v>22.156099999999999</v>
+      </c>
+      <c r="G9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="9">
+        <v>29</v>
+      </c>
+      <c r="J9" s="9">
         <v>9</v>
       </c>
-      <c r="K9" s="6">
-        <v>2016</v>
+      <c r="K9" s="9">
+        <v>2015</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="7">
-        <v>0.81</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>29</v>
+        <v>137</v>
+      </c>
+      <c r="M9" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="17">
-        <v>32</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="5">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D10" s="9">
+        <v>4</v>
       </c>
       <c r="E10" s="18">
-        <v>55.95984206</v>
+        <v>55.2913</v>
       </c>
       <c r="F10" s="18">
-        <v>25.43206404</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="6">
+        <v>21.377199999999998</v>
+      </c>
+      <c r="G10" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="I10" s="9">
         <v>4</v>
       </c>
-      <c r="J10" s="6">
+      <c r="J10" s="9">
         <v>10</v>
       </c>
-      <c r="K10" s="6">
-        <v>2022</v>
+      <c r="K10" s="9">
+        <v>2017</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0.54</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>45</v>
+        <v>166</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="17">
-        <v>44</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="5">
-        <v>1</v>
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D11" s="9">
+        <v>5</v>
       </c>
       <c r="E11" s="18">
-        <v>55.95984206</v>
+        <v>56.228900000000003</v>
       </c>
       <c r="F11" s="18">
-        <v>25.43206404</v>
-      </c>
-      <c r="G11" s="5" t="s">
+        <v>24.407499999999999</v>
+      </c>
+      <c r="G11" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="6">
-        <v>27</v>
-      </c>
-      <c r="J11" s="6">
+      <c r="H11" s="13" t="s">
+        <v>213</v>
+      </c>
+      <c r="I11" s="9">
+        <v>21</v>
+      </c>
+      <c r="J11" s="9">
         <v>9</v>
       </c>
-      <c r="K11" s="6">
-        <v>2016</v>
+      <c r="K11" s="9">
+        <v>2020</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="7">
-        <v>0.64</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>26</v>
+        <v>214</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="17">
-        <v>46</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1</v>
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2</v>
       </c>
       <c r="E12" s="18">
-        <v>55.95984206</v>
+        <v>56.050400000000003</v>
       </c>
       <c r="F12" s="18">
-        <v>25.43206404</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I12" s="6">
-        <v>25</v>
-      </c>
-      <c r="J12" s="6">
-        <v>9</v>
-      </c>
-      <c r="K12" s="6">
-        <v>2019</v>
+        <v>22.9727</v>
+      </c>
+      <c r="G12" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="9">
+        <v>8</v>
+      </c>
+      <c r="J12" s="9">
+        <v>10</v>
+      </c>
+      <c r="K12" s="9">
+        <v>2015</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="M12" s="7">
-        <v>0.66</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>26</v>
+        <v>115</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="17">
-        <v>29</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13" s="5">
-        <v>1</v>
+        <v>12</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="D13" s="9">
+        <v>2</v>
       </c>
       <c r="E13" s="18">
-        <v>56.124192209999997</v>
+        <v>56.050400000000003</v>
       </c>
       <c r="F13" s="18">
-        <v>21.263878009999999</v>
-      </c>
-      <c r="G13" s="5" t="s">
+        <v>22.9727</v>
+      </c>
+      <c r="G13" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" s="6">
-        <v>22</v>
-      </c>
-      <c r="J13" s="6">
-        <v>9</v>
-      </c>
-      <c r="K13" s="6">
-        <v>2022</v>
+      <c r="H13" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I13" s="9">
+        <v>12</v>
+      </c>
+      <c r="J13" s="9">
+        <v>10</v>
+      </c>
+      <c r="K13" s="9">
+        <v>2020</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="7">
-        <v>0.52</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>45</v>
+        <v>117</v>
+      </c>
+      <c r="M13" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="17">
-        <v>42</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="5">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D14" s="9">
+        <v>3</v>
       </c>
       <c r="E14" s="18">
-        <v>56.124192209999997</v>
+        <v>55.5124</v>
       </c>
       <c r="F14" s="18">
-        <v>21.263878009999999</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="6">
-        <v>20</v>
-      </c>
-      <c r="J14" s="6">
+        <v>23.964500000000001</v>
+      </c>
+      <c r="G14" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I14" s="9">
+        <v>28</v>
+      </c>
+      <c r="J14" s="9">
         <v>9</v>
       </c>
-      <c r="K14" s="6">
-        <v>2016</v>
+      <c r="K14" s="9">
+        <v>2021</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="M14" s="7">
-        <v>0.6</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>26</v>
+        <v>158</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="17">
-        <v>74</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="D15" s="5">
-        <v>1</v>
+        <v>14</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="9">
+        <v>5</v>
       </c>
       <c r="E15" s="18">
-        <v>56.124192209999997</v>
+        <v>56.228900000000003</v>
       </c>
       <c r="F15" s="18">
-        <v>21.263878009999999</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H15" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="I15" s="6">
-        <v>9</v>
-      </c>
-      <c r="J15" s="6">
+        <v>24.407499999999999</v>
+      </c>
+      <c r="G15" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="I15" s="9">
+        <v>16</v>
+      </c>
+      <c r="J15" s="9">
         <v>10</v>
       </c>
-      <c r="K15" s="6">
-        <v>2019</v>
+      <c r="K15" s="9">
+        <v>2017</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M15" s="7">
-        <v>0.83</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>29</v>
+        <v>216</v>
+      </c>
+      <c r="M15" s="10">
+        <v>0.38</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="17">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>59</v>
+        <v>135</v>
       </c>
       <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="19">
-        <v>55.842799999999997</v>
-      </c>
-      <c r="F16" s="19">
-        <v>23.886399999999998</v>
-      </c>
-      <c r="G16" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>60</v>
+        <v>3</v>
+      </c>
+      <c r="E16" s="18">
+        <v>55.479500000000002</v>
+      </c>
+      <c r="F16" s="18">
+        <v>22.156099999999999</v>
+      </c>
+      <c r="G16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="I16" s="9">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J16" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K16" s="9">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="M16" s="10">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="N16" s="10" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="17">
-        <v>49</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1</v>
+        <v>16</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D17" s="9">
+        <v>3</v>
       </c>
       <c r="E17" s="18">
-        <v>54.353197020000003</v>
+        <v>55.5124</v>
       </c>
       <c r="F17" s="18">
-        <v>24.83006962</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="6">
-        <v>2</v>
-      </c>
-      <c r="J17" s="6">
-        <v>10</v>
-      </c>
-      <c r="K17" s="6">
-        <v>2019</v>
+        <v>23.964500000000001</v>
+      </c>
+      <c r="G17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="9">
+        <v>30</v>
+      </c>
+      <c r="J17" s="9">
+        <v>9</v>
+      </c>
+      <c r="K17" s="9">
+        <v>2015</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="M17" s="7">
-        <v>0.68</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>26</v>
+        <v>159</v>
+      </c>
+      <c r="M17" s="10">
+        <v>0.39</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="17">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>63</v>
+        <v>148</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
       <c r="D18" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="18">
-        <v>54.353197020000003</v>
+        <v>56.256980110000001</v>
       </c>
       <c r="F18" s="18">
-        <v>24.83006962</v>
+        <v>21.64241196</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H18" s="12" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="I18" s="6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J18" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K18" s="6">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>68</v>
+        <v>151</v>
       </c>
       <c r="M18" s="7">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="17">
-        <v>77</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1</v>
+        <v>18</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="9">
+        <v>3</v>
       </c>
       <c r="E19" s="18">
-        <v>54.353197020000003</v>
+        <v>55.5124</v>
       </c>
       <c r="F19" s="18">
-        <v>24.83006962</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="6">
-        <v>18</v>
-      </c>
-      <c r="J19" s="6">
+        <v>23.964500000000001</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19" s="16">
+        <v>4</v>
+      </c>
+      <c r="J19" s="16">
         <v>10</v>
       </c>
-      <c r="K19" s="6">
-        <v>2016</v>
+      <c r="K19" s="9">
+        <v>2018</v>
       </c>
       <c r="L19" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="M19" s="7">
-        <v>0.88</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>29</v>
+        <v>161</v>
+      </c>
+      <c r="M19" s="10">
+        <v>0.41</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="17">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D20" s="5">
+        <v>4</v>
+      </c>
+      <c r="E20" s="18">
+        <v>54.687280209999997</v>
+      </c>
+      <c r="F20" s="18">
+        <v>25.080435420000001</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="I20" s="6">
         <v>3</v>
       </c>
-      <c r="B20" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="9">
-        <v>1</v>
-      </c>
-      <c r="E20" s="18">
-        <v>55.780200000000001</v>
-      </c>
-      <c r="F20" s="18">
-        <v>21.2561</v>
-      </c>
-      <c r="G20" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="9">
-        <v>21</v>
-      </c>
-      <c r="J20" s="9">
-        <v>9</v>
-      </c>
-      <c r="K20" s="9">
-        <v>2021</v>
+      <c r="J20" s="6">
+        <v>10</v>
+      </c>
+      <c r="K20" s="6">
+        <v>2022</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="M20" s="10">
-        <v>0.31</v>
-      </c>
-      <c r="N20" s="10" t="s">
-        <v>19</v>
+        <v>172</v>
+      </c>
+      <c r="M20" s="7">
+        <v>0.42</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="17">
-        <v>7</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="9">
-        <v>1</v>
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D21" s="5">
+        <v>5</v>
       </c>
       <c r="E21" s="18">
-        <v>55.780200000000001</v>
+        <v>56.0705004</v>
       </c>
       <c r="F21" s="18">
-        <v>21.2561</v>
-      </c>
-      <c r="G21" t="s">
-        <v>16</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="I21" s="9">
-        <v>18</v>
-      </c>
-      <c r="J21" s="9">
-        <v>9</v>
-      </c>
-      <c r="K21" s="9">
-        <v>2018</v>
+        <v>24.086051139999999</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H21" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="6">
+        <v>3</v>
+      </c>
+      <c r="J21" s="6">
+        <v>10</v>
+      </c>
+      <c r="K21" s="6">
+        <v>2016</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="M21" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>19</v>
+        <v>191</v>
+      </c>
+      <c r="M21" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="17">
-        <v>2</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D22" s="9">
-        <v>1</v>
-      </c>
-      <c r="E22" s="19">
-        <v>55.266034769999997</v>
-      </c>
-      <c r="F22" s="19">
-        <v>21.454944709999999</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="I22" s="9">
-        <v>14</v>
-      </c>
-      <c r="J22" s="9">
-        <v>9</v>
-      </c>
-      <c r="K22" s="9">
-        <v>2015</v>
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D22" s="5">
+        <v>4</v>
+      </c>
+      <c r="E22" s="18">
+        <v>56.128425649999997</v>
+      </c>
+      <c r="F22" s="18">
+        <v>24.451966899999999</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H22" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I22" s="6">
+        <v>3</v>
+      </c>
+      <c r="J22" s="6">
+        <v>10</v>
+      </c>
+      <c r="K22" s="6">
+        <v>2016</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M22" s="10">
-        <v>0.28999999999999998</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>62</v>
+        <v>181</v>
+      </c>
+      <c r="M22" s="7">
+        <v>0.46</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="17">
-        <v>58</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="5">
-        <v>2</v>
+        <v>22</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D23" s="9">
+        <v>4</v>
       </c>
       <c r="E23" s="18">
-        <v>55.91262141</v>
+        <v>55.2913</v>
       </c>
       <c r="F23" s="18">
-        <v>21.780353040000001</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I23" s="6">
-        <v>1</v>
-      </c>
-      <c r="J23" s="6">
-        <v>10</v>
-      </c>
-      <c r="K23" s="6">
-        <v>2019</v>
+        <v>21.377199999999998</v>
+      </c>
+      <c r="G23" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="I23" s="16">
+        <v>14</v>
+      </c>
+      <c r="J23" s="16">
+        <v>9</v>
+      </c>
+      <c r="K23" s="9">
+        <v>2020</v>
       </c>
       <c r="L23" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="M23" s="7">
-        <v>0.72</v>
-      </c>
-      <c r="N23" s="7" t="s">
-        <v>26</v>
+        <v>168</v>
+      </c>
+      <c r="M23" s="10">
+        <v>0.48</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="17">
-        <v>70</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D24" s="5">
-        <v>2</v>
+        <v>23</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="9">
+        <v>5</v>
       </c>
       <c r="E24" s="18">
-        <v>55.91262141</v>
+        <v>56.228900000000003</v>
       </c>
       <c r="F24" s="18">
-        <v>21.780353040000001</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="I24" s="6">
-        <v>5</v>
-      </c>
-      <c r="J24" s="6">
-        <v>10</v>
-      </c>
-      <c r="K24" s="6">
-        <v>2022</v>
+        <v>24.407499999999999</v>
+      </c>
+      <c r="G24" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="I24" s="9">
+        <v>26</v>
+      </c>
+      <c r="J24" s="9">
+        <v>9</v>
+      </c>
+      <c r="K24" s="9">
+        <v>2016</v>
       </c>
       <c r="L24" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="M24" s="7">
-        <v>0.79</v>
-      </c>
-      <c r="N24" s="7" t="s">
-        <v>26</v>
+        <v>217</v>
+      </c>
+      <c r="M24" s="10">
+        <v>0.48</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="17">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="D25" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E25" s="18">
-        <v>55.91262141</v>
+        <v>56.0705004</v>
       </c>
       <c r="F25" s="18">
-        <v>21.780353040000001</v>
+        <v>24.086051139999999</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H25" s="12" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="I25" s="6">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J25" s="6">
         <v>10</v>
       </c>
       <c r="K25" s="6">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="L25" s="9" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="M25" s="7">
-        <v>0.92</v>
+        <v>0.49</v>
       </c>
       <c r="N25" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="17">
-        <v>51</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="5">
-        <v>2</v>
+        <v>25</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="D26" s="9">
+        <v>3</v>
       </c>
       <c r="E26" s="18">
-        <v>54.341399729999999</v>
+        <v>55.479500000000002</v>
       </c>
       <c r="F26" s="18">
-        <v>24.88637937</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="6">
-        <v>14</v>
-      </c>
-      <c r="J26" s="6">
-        <v>10</v>
-      </c>
-      <c r="K26" s="6">
-        <v>2015</v>
+        <v>22.156099999999999</v>
+      </c>
+      <c r="G26" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="16">
+        <v>23</v>
+      </c>
+      <c r="J26" s="16">
+        <v>9</v>
+      </c>
+      <c r="K26" s="9">
+        <v>2021</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="M26" s="7">
-        <v>0.69</v>
-      </c>
-      <c r="N26" s="7" t="s">
-        <v>26</v>
+        <v>141</v>
+      </c>
+      <c r="M26" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="17">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>89</v>
+        <v>190</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="D27" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E27" s="18">
-        <v>54.341399729999999</v>
+        <v>56.0705004</v>
       </c>
       <c r="F27" s="18">
-        <v>24.88637937</v>
+        <v>24.086051139999999</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H27" s="12" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="I27" s="6">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="J27" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K27" s="6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="L27" s="9" t="s">
-        <v>93</v>
+        <v>193</v>
       </c>
       <c r="M27" s="7">
-        <v>0.69</v>
+        <v>0.5</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="17">
-        <v>76</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D28" s="5">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="D28" s="9">
+        <v>5</v>
       </c>
       <c r="E28" s="18">
-        <v>54.341399729999999</v>
+        <v>56.228900000000003</v>
       </c>
       <c r="F28" s="18">
-        <v>24.88637937</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="I28" s="6">
-        <v>11</v>
-      </c>
-      <c r="J28" s="6">
-        <v>10</v>
-      </c>
-      <c r="K28" s="6">
-        <v>2022</v>
+        <v>24.407499999999999</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="I28" s="16">
+        <v>28</v>
+      </c>
+      <c r="J28" s="16">
+        <v>9</v>
+      </c>
+      <c r="K28" s="9">
+        <v>2015</v>
       </c>
       <c r="L28" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="M28" s="7">
-        <v>0.86</v>
-      </c>
-      <c r="N28" s="7" t="s">
-        <v>29</v>
+        <v>218</v>
+      </c>
+      <c r="M28" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="17">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>96</v>
+        <v>169</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>97</v>
+        <v>170</v>
       </c>
       <c r="D29" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E29" s="18">
-        <v>55.080792750000001</v>
+        <v>54.687280209999997</v>
       </c>
       <c r="F29" s="18">
-        <v>22.743415259999999</v>
+        <v>25.080435420000001</v>
       </c>
       <c r="G29" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="12" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="I29" s="6">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J29" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" s="6">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="M29" s="7">
-        <v>0.59</v>
+        <v>0.51</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>45</v>
@@ -2431,131 +2431,131 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="17">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30" s="5">
+        <v>1</v>
+      </c>
+      <c r="E30" s="18">
+        <v>56.124192209999997</v>
+      </c>
+      <c r="F30" s="18">
+        <v>21.263878009999999</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H30" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="6">
+        <v>22</v>
+      </c>
+      <c r="J30" s="6">
+        <v>9</v>
+      </c>
+      <c r="K30" s="6">
+        <v>2022</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="7">
+        <v>0.52</v>
+      </c>
+      <c r="N30" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="D30" s="5">
-        <v>2</v>
-      </c>
-      <c r="E30" s="18">
-        <v>55.080792750000001</v>
-      </c>
-      <c r="F30" s="18">
-        <v>22.743415259999999</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H30" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="I30" s="6">
-        <v>3</v>
-      </c>
-      <c r="J30" s="6">
-        <v>10</v>
-      </c>
-      <c r="K30" s="6">
-        <v>2019</v>
-      </c>
-      <c r="L30" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="M30" s="7">
-        <v>0.65</v>
-      </c>
-      <c r="N30" s="7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="17">
-        <v>72</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>96</v>
+        <v>179</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>97</v>
+        <v>180</v>
       </c>
       <c r="D31" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E31" s="18">
-        <v>55.080792750000001</v>
+        <v>56.128425649999997</v>
       </c>
       <c r="F31" s="18">
-        <v>22.743415259999999</v>
+        <v>24.451966899999999</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H31" s="12" t="s">
-        <v>101</v>
+        <v>171</v>
       </c>
       <c r="I31" s="6">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="J31" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" s="6">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="L31" s="9" t="s">
-        <v>102</v>
+        <v>182</v>
       </c>
       <c r="M31" s="7">
-        <v>0.82</v>
+        <v>0.52</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="17">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="D32" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E32" s="18">
-        <v>55.250778369999999</v>
+        <v>56.128425649999997</v>
       </c>
       <c r="F32" s="18">
-        <v>26.600762320000001</v>
+        <v>24.451966899999999</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="H32" s="12" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I32" s="6">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J32" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K32" s="6">
         <v>2019</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="M32" s="7">
-        <v>0.56999999999999995</v>
+        <v>0.53</v>
       </c>
       <c r="N32" s="7" t="s">
         <v>45</v>
@@ -2563,351 +2563,351 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="17">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>103</v>
+        <v>40</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>104</v>
+        <v>41</v>
       </c>
       <c r="D33" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="18">
-        <v>55.250778369999999</v>
+        <v>55.95984206</v>
       </c>
       <c r="F33" s="18">
-        <v>26.600762320000001</v>
+        <v>25.43206404</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="H33" s="12" t="s">
-        <v>108</v>
+        <v>43</v>
       </c>
       <c r="I33" s="6">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="J33" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K33" s="6">
         <v>2022</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>109</v>
+        <v>44</v>
       </c>
       <c r="M33" s="7">
-        <v>0.74</v>
+        <v>0.54</v>
       </c>
       <c r="N33" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="17">
-        <v>67</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="D34" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E34" s="18">
-        <v>55.250778369999999</v>
+        <v>55.579729479999997</v>
       </c>
       <c r="F34" s="18">
-        <v>26.600762320000001</v>
+        <v>21.565642820000001</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>105</v>
+        <v>16</v>
       </c>
       <c r="H34" s="12" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="I34" s="6">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J34" s="6">
         <v>9</v>
       </c>
       <c r="K34" s="6">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="L34" s="9" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="M34" s="7">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
       <c r="N34" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="17">
-        <v>11</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D35" s="9">
-        <v>2</v>
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" s="5">
+        <v>5</v>
       </c>
       <c r="E35" s="18">
-        <v>56.050400000000003</v>
+        <v>55.621911740000002</v>
       </c>
       <c r="F35" s="18">
-        <v>22.9727</v>
-      </c>
-      <c r="G35" t="s">
-        <v>52</v>
-      </c>
-      <c r="H35" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="I35" s="9">
-        <v>8</v>
-      </c>
-      <c r="J35" s="9">
-        <v>10</v>
-      </c>
-      <c r="K35" s="9">
-        <v>2015</v>
+        <v>25.5652358</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H35" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="6">
+        <v>18</v>
+      </c>
+      <c r="J35" s="6">
+        <v>9</v>
+      </c>
+      <c r="K35" s="6">
+        <v>2019</v>
       </c>
       <c r="L35" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="M35" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="N35" s="10" t="s">
-        <v>19</v>
+        <v>202</v>
+      </c>
+      <c r="M35" s="7">
+        <v>0.54</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="17">
-        <v>12</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="C36" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="D36" s="9">
-        <v>2</v>
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D36" s="5">
+        <v>5</v>
       </c>
       <c r="E36" s="18">
-        <v>56.050400000000003</v>
+        <v>54.308265929999997</v>
       </c>
       <c r="F36" s="18">
-        <v>22.9727</v>
-      </c>
-      <c r="G36" t="s">
-        <v>52</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="I36" s="9">
-        <v>12</v>
-      </c>
-      <c r="J36" s="9">
+        <v>24.661928849999999</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H36" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="I36" s="6">
         <v>10</v>
       </c>
-      <c r="K36" s="9">
-        <v>2020</v>
+      <c r="J36" s="6">
+        <v>10</v>
+      </c>
+      <c r="K36" s="6">
+        <v>2019</v>
       </c>
       <c r="L36" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="M36" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="N36" s="10" t="s">
-        <v>19</v>
+        <v>187</v>
+      </c>
+      <c r="M36" s="7">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="17">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>118</v>
+        <v>103</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="D37" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E37" s="18">
-        <v>54.201132620000003</v>
+        <v>55.250778369999999</v>
       </c>
       <c r="F37" s="18">
-        <v>24.371298920000001</v>
+        <v>26.600762320000001</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>16</v>
+        <v>105</v>
       </c>
       <c r="H37" s="12" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="I37" s="6">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J37" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K37" s="6">
         <v>2019</v>
       </c>
       <c r="L37" s="9" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="M37" s="7">
-        <v>0.82</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N37" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="17">
-        <v>79</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>118</v>
+        <v>194</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>119</v>
+        <v>195</v>
       </c>
       <c r="D38" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E38" s="18">
-        <v>54.201132620000003</v>
+        <v>55.929042940000002</v>
       </c>
       <c r="F38" s="18">
-        <v>24.371298920000001</v>
+        <v>24.291695959999998</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H38" s="12" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="I38" s="6">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="J38" s="6">
         <v>10</v>
       </c>
       <c r="K38" s="6">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="L38" s="9" t="s">
-        <v>123</v>
+        <v>196</v>
       </c>
       <c r="M38" s="7">
-        <v>0.93</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N38" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="17">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>118</v>
+        <v>206</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>119</v>
+        <v>207</v>
       </c>
       <c r="D39" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E39" s="18">
-        <v>54.201132620000003</v>
+        <v>54.755648749999999</v>
       </c>
       <c r="F39" s="18">
-        <v>24.371298920000001</v>
+        <v>22.987372709999999</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H39" s="12" t="s">
-        <v>124</v>
+        <v>208</v>
       </c>
       <c r="I39" s="6">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J39" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K39" s="6">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="L39" s="9" t="s">
-        <v>125</v>
+        <v>209</v>
       </c>
       <c r="M39" s="7">
-        <v>1</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N39" s="7" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D40" s="5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E40" s="18">
-        <v>55.579729479999997</v>
+        <v>55.080792750000001</v>
       </c>
       <c r="F40" s="18">
-        <v>21.565642820000001</v>
+        <v>22.743415259999999</v>
       </c>
       <c r="G40" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H40" s="12" t="s">
-        <v>128</v>
+        <v>27</v>
       </c>
       <c r="I40" s="6">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="J40" s="6">
         <v>9</v>
       </c>
       <c r="K40" s="6">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="L40" s="9" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="M40" s="7">
-        <v>0.54</v>
+        <v>0.59</v>
       </c>
       <c r="N40" s="7" t="s">
         <v>45</v>
@@ -2959,219 +2959,219 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="17">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>126</v>
+        <v>200</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>127</v>
+        <v>201</v>
       </c>
       <c r="D42" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E42" s="18">
-        <v>55.579729479999997</v>
+        <v>55.621911740000002</v>
       </c>
       <c r="F42" s="18">
-        <v>21.565642820000001</v>
+        <v>25.5652358</v>
       </c>
       <c r="G42" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>132</v>
+        <v>203</v>
       </c>
       <c r="I42" s="6">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J42" s="6">
         <v>9</v>
       </c>
       <c r="K42" s="6">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="L42" s="9" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="M42" s="7">
-        <v>0.7</v>
+        <v>0.59</v>
       </c>
       <c r="N42" s="7" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="17">
-        <v>8</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C43" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D43" s="9">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="5">
+        <v>1</v>
       </c>
       <c r="E43" s="18">
-        <v>55.479500000000002</v>
+        <v>56.124192209999997</v>
       </c>
       <c r="F43" s="18">
-        <v>22.156099999999999</v>
-      </c>
-      <c r="G43" t="s">
-        <v>16</v>
-      </c>
-      <c r="H43" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="I43" s="9">
-        <v>29</v>
-      </c>
-      <c r="J43" s="9">
+        <v>21.263878009999999</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H43" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="6">
+        <v>20</v>
+      </c>
+      <c r="J43" s="6">
         <v>9</v>
       </c>
-      <c r="K43" s="9">
-        <v>2015</v>
+      <c r="K43" s="6">
+        <v>2016</v>
       </c>
       <c r="L43" s="9" t="s">
-        <v>137</v>
-      </c>
-      <c r="M43" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="N43" s="10" t="s">
-        <v>19</v>
+        <v>55</v>
+      </c>
+      <c r="M43" s="7">
+        <v>0.6</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="17">
-        <v>15</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C44" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D44" s="9">
-        <v>3</v>
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D44" s="5">
+        <v>4</v>
       </c>
       <c r="E44" s="18">
-        <v>55.479500000000002</v>
+        <v>54.687280209999997</v>
       </c>
       <c r="F44" s="18">
-        <v>22.156099999999999</v>
-      </c>
-      <c r="G44" t="s">
-        <v>16</v>
-      </c>
-      <c r="H44" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="I44" s="9">
-        <v>19</v>
-      </c>
-      <c r="J44" s="9">
-        <v>9</v>
-      </c>
-      <c r="K44" s="9">
-        <v>2018</v>
+        <v>25.080435420000001</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="I44" s="6">
+        <v>5</v>
+      </c>
+      <c r="J44" s="6">
+        <v>10</v>
+      </c>
+      <c r="K44" s="6">
+        <v>2015</v>
       </c>
       <c r="L44" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="M44" s="10">
-        <v>0.39</v>
-      </c>
-      <c r="N44" s="10" t="s">
-        <v>19</v>
+        <v>176</v>
+      </c>
+      <c r="M44" s="7">
+        <v>0.62</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="17">
-        <v>25</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>134</v>
-      </c>
-      <c r="C45" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="D45" s="9">
-        <v>3</v>
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" s="5">
+        <v>1</v>
       </c>
       <c r="E45" s="18">
-        <v>55.479500000000002</v>
+        <v>55.95984206</v>
       </c>
       <c r="F45" s="18">
-        <v>22.156099999999999</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H45" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="I45" s="16">
-        <v>23</v>
-      </c>
-      <c r="J45" s="16">
+        <v>25.43206404</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H45" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="I45" s="6">
+        <v>27</v>
+      </c>
+      <c r="J45" s="6">
         <v>9</v>
       </c>
-      <c r="K45" s="9">
-        <v>2021</v>
+      <c r="K45" s="6">
+        <v>2016</v>
       </c>
       <c r="L45" s="9" t="s">
-        <v>141</v>
-      </c>
-      <c r="M45" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="N45" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="M45" s="7">
+        <v>0.64</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="17">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="D46" s="5">
+        <v>2</v>
+      </c>
+      <c r="E46" s="18">
+        <v>55.080792750000001</v>
+      </c>
+      <c r="F46" s="18">
+        <v>22.743415259999999</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="I46" s="6">
         <v>3</v>
       </c>
-      <c r="E46" s="18">
-        <v>55.774891099999998</v>
-      </c>
-      <c r="F46" s="18">
-        <v>24.74461586</v>
-      </c>
-      <c r="G46" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="I46" s="6">
-        <v>25</v>
-      </c>
       <c r="J46" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K46" s="6">
         <v>2019</v>
       </c>
       <c r="L46" s="9" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="M46" s="7">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="N46" s="7" t="s">
         <v>26</v>
@@ -3179,43 +3179,43 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="17">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>143</v>
+        <v>41</v>
       </c>
       <c r="D47" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E47" s="18">
-        <v>55.774891099999998</v>
+        <v>55.95984206</v>
       </c>
       <c r="F47" s="18">
-        <v>24.74461586</v>
+        <v>25.43206404</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H47" s="12" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I47" s="6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J47" s="6">
         <v>9</v>
       </c>
       <c r="K47" s="6">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>145</v>
+        <v>49</v>
       </c>
       <c r="M47" s="7">
-        <v>0.69</v>
+        <v>0.66</v>
       </c>
       <c r="N47" s="7" t="s">
         <v>26</v>
@@ -3223,7 +3223,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="17">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>142</v>
@@ -3244,22 +3244,22 @@
         <v>42</v>
       </c>
       <c r="H48" s="12" t="s">
-        <v>146</v>
+        <v>48</v>
       </c>
       <c r="I48" s="6">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J48" s="6">
         <v>9</v>
       </c>
       <c r="K48" s="6">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="L48" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M48" s="7">
-        <v>0.74</v>
+        <v>0.66</v>
       </c>
       <c r="N48" s="7" t="s">
         <v>26</v>
@@ -3267,75 +3267,75 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="17">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="D49" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E49" s="18">
-        <v>56.256980110000001</v>
+        <v>55.929042940000002</v>
       </c>
       <c r="F49" s="18">
-        <v>21.64241196</v>
+        <v>24.291695959999998</v>
       </c>
       <c r="G49" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="H49" s="12" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="I49" s="6">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J49" s="6">
         <v>9</v>
       </c>
       <c r="K49" s="6">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="M49" s="7">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="N49" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="17">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>149</v>
+        <v>64</v>
       </c>
       <c r="D50" s="5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E50" s="18">
-        <v>56.256980110000001</v>
+        <v>54.353197020000003</v>
       </c>
       <c r="F50" s="18">
-        <v>21.64241196</v>
+        <v>24.83006962</v>
       </c>
       <c r="G50" s="5" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>152</v>
+        <v>65</v>
       </c>
       <c r="I50" s="6">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="J50" s="6">
         <v>10</v>
@@ -3344,10 +3344,10 @@
         <v>2019</v>
       </c>
       <c r="L50" s="9" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="M50" s="7">
-        <v>0.69</v>
+        <v>0.68</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>26</v>
@@ -3355,383 +3355,383 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="17">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="D51" s="5">
+        <v>4</v>
+      </c>
+      <c r="E51" s="18">
+        <v>54.687280209999997</v>
+      </c>
+      <c r="F51" s="18">
+        <v>25.080435420000001</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H51" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="I51" s="6">
         <v>3</v>
       </c>
-      <c r="E51" s="18">
-        <v>56.256980110000001</v>
-      </c>
-      <c r="F51" s="18">
-        <v>21.64241196</v>
-      </c>
-      <c r="G51" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H51" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="I51" s="6">
-        <v>27</v>
-      </c>
       <c r="J51" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K51" s="6">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="L51" s="9" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="M51" s="7">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="N51" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="17">
-        <v>13</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C52" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D52" s="9">
-        <v>3</v>
+        <v>51</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D52" s="5">
+        <v>2</v>
       </c>
       <c r="E52" s="18">
-        <v>55.5124</v>
+        <v>54.341399729999999</v>
       </c>
       <c r="F52" s="18">
-        <v>23.964500000000001</v>
-      </c>
-      <c r="G52" t="s">
-        <v>16</v>
-      </c>
-      <c r="H52" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="I52" s="9">
-        <v>28</v>
-      </c>
-      <c r="J52" s="9">
-        <v>9</v>
-      </c>
-      <c r="K52" s="9">
-        <v>2021</v>
+        <v>24.88637937</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H52" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="I52" s="6">
+        <v>14</v>
+      </c>
+      <c r="J52" s="6">
+        <v>10</v>
+      </c>
+      <c r="K52" s="6">
+        <v>2015</v>
       </c>
       <c r="L52" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="M52" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="N52" s="10" t="s">
-        <v>19</v>
+        <v>92</v>
+      </c>
+      <c r="M52" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="17">
-        <v>16</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C53" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D53" s="9">
-        <v>3</v>
+        <v>52</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D53" s="5">
+        <v>2</v>
       </c>
       <c r="E53" s="18">
-        <v>55.5124</v>
+        <v>54.341399729999999</v>
       </c>
       <c r="F53" s="18">
-        <v>23.964500000000001</v>
-      </c>
-      <c r="G53" t="s">
-        <v>16</v>
-      </c>
-      <c r="H53" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="I53" s="9">
-        <v>30</v>
-      </c>
-      <c r="J53" s="9">
-        <v>9</v>
-      </c>
-      <c r="K53" s="9">
-        <v>2015</v>
+        <v>24.88637937</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H53" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I53" s="6">
+        <v>2</v>
+      </c>
+      <c r="J53" s="6">
+        <v>10</v>
+      </c>
+      <c r="K53" s="6">
+        <v>2019</v>
       </c>
       <c r="L53" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="M53" s="10">
-        <v>0.39</v>
-      </c>
-      <c r="N53" s="10" t="s">
-        <v>19</v>
+        <v>93</v>
+      </c>
+      <c r="M53" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="17">
-        <v>18</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C54" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="D54" s="9">
+        <v>53</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="5">
         <v>3</v>
       </c>
       <c r="E54" s="18">
-        <v>55.5124</v>
+        <v>55.774891099999998</v>
       </c>
       <c r="F54" s="18">
-        <v>23.964500000000001</v>
-      </c>
-      <c r="G54" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H54" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="I54" s="16">
-        <v>4</v>
-      </c>
-      <c r="J54" s="16">
-        <v>10</v>
-      </c>
-      <c r="K54" s="9">
-        <v>2018</v>
+        <v>24.74461586</v>
+      </c>
+      <c r="G54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="H54" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I54" s="6">
+        <v>28</v>
+      </c>
+      <c r="J54" s="6">
+        <v>9</v>
+      </c>
+      <c r="K54" s="6">
+        <v>2016</v>
       </c>
       <c r="L54" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="M54" s="10">
-        <v>0.41</v>
-      </c>
-      <c r="N54" s="10" t="s">
-        <v>45</v>
+        <v>145</v>
+      </c>
+      <c r="M54" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="17">
-        <v>4</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" s="9">
-        <v>4</v>
+        <v>54</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" s="5">
+        <v>3</v>
       </c>
       <c r="E55" s="18">
-        <v>55.2913</v>
+        <v>56.256980110000001</v>
       </c>
       <c r="F55" s="18">
-        <v>21.377199999999998</v>
-      </c>
-      <c r="G55" t="s">
-        <v>16</v>
-      </c>
-      <c r="H55" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="I55" s="9">
-        <v>12</v>
-      </c>
-      <c r="J55" s="9">
+        <v>21.64241196</v>
+      </c>
+      <c r="G55" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H55" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="I55" s="6">
+        <v>21</v>
+      </c>
+      <c r="J55" s="6">
         <v>10</v>
       </c>
-      <c r="K55" s="9">
-        <v>2015</v>
+      <c r="K55" s="6">
+        <v>2019</v>
       </c>
       <c r="L55" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="M55" s="10">
-        <v>0.31</v>
-      </c>
-      <c r="N55" s="10" t="s">
-        <v>19</v>
+        <v>153</v>
+      </c>
+      <c r="M55" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="17">
-        <v>9</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C56" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D56" s="9">
-        <v>4</v>
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="D56" s="5">
+        <v>5</v>
       </c>
       <c r="E56" s="18">
-        <v>55.2913</v>
+        <v>54.308265929999997</v>
       </c>
       <c r="F56" s="18">
-        <v>21.377199999999998</v>
-      </c>
-      <c r="G56" t="s">
-        <v>16</v>
-      </c>
-      <c r="H56" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="I56" s="9">
-        <v>4</v>
-      </c>
-      <c r="J56" s="9">
+        <v>24.661928849999999</v>
+      </c>
+      <c r="G56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H56" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="I56" s="6">
+        <v>14</v>
+      </c>
+      <c r="J56" s="6">
         <v>10</v>
       </c>
-      <c r="K56" s="9">
-        <v>2017</v>
+      <c r="K56" s="6">
+        <v>2015</v>
       </c>
       <c r="L56" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="M56" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="N56" s="10" t="s">
-        <v>19</v>
+        <v>188</v>
+      </c>
+      <c r="M56" s="7">
+        <v>0.69</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="17">
-        <v>22</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="C57" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="D57" s="9">
-        <v>4</v>
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D57" s="5">
+        <v>3</v>
       </c>
       <c r="E57" s="18">
-        <v>55.2913</v>
+        <v>55.579729479999997</v>
       </c>
       <c r="F57" s="18">
-        <v>21.377199999999998</v>
-      </c>
-      <c r="G57" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H57" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="I57" s="16">
-        <v>14</v>
-      </c>
-      <c r="J57" s="16">
+        <v>21.565642820000001</v>
+      </c>
+      <c r="G57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="I57" s="6">
+        <v>27</v>
+      </c>
+      <c r="J57" s="6">
         <v>9</v>
       </c>
-      <c r="K57" s="9">
-        <v>2020</v>
+      <c r="K57" s="6">
+        <v>2022</v>
       </c>
       <c r="L57" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="M57" s="10">
-        <v>0.48</v>
-      </c>
-      <c r="N57" s="10" t="s">
-        <v>45</v>
+        <v>133</v>
+      </c>
+      <c r="M57" s="7">
+        <v>0.7</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="17">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>169</v>
+        <v>200</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D58" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E58" s="18">
-        <v>54.687280209999997</v>
+        <v>55.621911740000002</v>
       </c>
       <c r="F58" s="18">
-        <v>25.080435420000001</v>
+        <v>25.5652358</v>
       </c>
       <c r="G58" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H58" s="12" t="s">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="I58" s="6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J58" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K58" s="6">
         <v>2022</v>
       </c>
       <c r="L58" s="9" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
       <c r="M58" s="7">
-        <v>0.42</v>
+        <v>0.71</v>
       </c>
       <c r="N58" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="17">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="D59" s="5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E59" s="18">
-        <v>54.687280209999997</v>
+        <v>55.91262141</v>
       </c>
       <c r="F59" s="18">
-        <v>25.080435420000001</v>
+        <v>21.780353040000001</v>
       </c>
       <c r="G59" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H59" s="12" t="s">
-        <v>173</v>
+        <v>83</v>
       </c>
       <c r="I59" s="6">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="J59" s="6">
         <v>10</v>
@@ -3740,42 +3740,42 @@
         <v>2019</v>
       </c>
       <c r="L59" s="9" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="M59" s="7">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="N59" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="17">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="D60" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E60" s="18">
-        <v>54.687280209999997</v>
+        <v>55.929042940000002</v>
       </c>
       <c r="F60" s="18">
-        <v>25.080435420000001</v>
+        <v>24.291695959999998</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="I60" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J60" s="6">
         <v>10</v>
@@ -3784,10 +3784,10 @@
         <v>2015</v>
       </c>
       <c r="L60" s="9" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="M60" s="7">
-        <v>0.62</v>
+        <v>0.72</v>
       </c>
       <c r="N60" s="7" t="s">
         <v>26</v>
@@ -3795,43 +3795,43 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="17">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>169</v>
+        <v>32</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>170</v>
+        <v>33</v>
       </c>
       <c r="D61" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E61" s="18">
-        <v>54.687280209999997</v>
+        <v>54.755461689999997</v>
       </c>
       <c r="F61" s="18">
-        <v>25.080435420000001</v>
+        <v>24.957577279999999</v>
       </c>
       <c r="G61" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>177</v>
+        <v>34</v>
       </c>
       <c r="I61" s="6">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="J61" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K61" s="6">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>178</v>
+        <v>35</v>
       </c>
       <c r="M61" s="7">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="N61" s="7" t="s">
         <v>26</v>
@@ -3839,219 +3839,219 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="17">
+        <v>61</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D62" s="5">
+        <v>2</v>
+      </c>
+      <c r="E62" s="18">
+        <v>55.250778369999999</v>
+      </c>
+      <c r="F62" s="18">
+        <v>26.600762320000001</v>
+      </c>
+      <c r="G62" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="H62" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="I62" s="6">
         <v>21</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D62" s="5">
-        <v>4</v>
-      </c>
-      <c r="E62" s="18">
-        <v>56.128425649999997</v>
-      </c>
-      <c r="F62" s="18">
-        <v>24.451966899999999</v>
-      </c>
-      <c r="G62" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H62" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="I62" s="6">
-        <v>3</v>
-      </c>
       <c r="J62" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K62" s="6">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="L62" s="9" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="M62" s="7">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="N62" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="17">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>179</v>
+        <v>142</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="D63" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E63" s="18">
-        <v>56.128425649999997</v>
+        <v>55.774891099999998</v>
       </c>
       <c r="F63" s="18">
-        <v>24.451966899999999</v>
+        <v>24.74461586</v>
       </c>
       <c r="G63" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>171</v>
+        <v>146</v>
       </c>
       <c r="I63" s="6">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="J63" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K63" s="6">
         <v>2022</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="M63" s="7">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
       <c r="N63" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="17">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>179</v>
+        <v>32</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>180</v>
+        <v>33</v>
       </c>
       <c r="D64" s="5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E64" s="18">
-        <v>56.128425649999997</v>
+        <v>54.755461689999997</v>
       </c>
       <c r="F64" s="18">
-        <v>24.451966899999999</v>
+        <v>24.957577279999999</v>
       </c>
       <c r="G64" s="5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="I64" s="6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J64" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K64" s="6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="L64" s="9" t="s">
-        <v>183</v>
+        <v>37</v>
       </c>
       <c r="M64" s="7">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="N64" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="17">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D65" s="5">
         <v>5</v>
       </c>
       <c r="E65" s="18">
-        <v>54.308265929999997</v>
+        <v>54.755648749999999</v>
       </c>
       <c r="F65" s="18">
-        <v>24.661928849999999</v>
+        <v>22.987372709999999</v>
       </c>
       <c r="G65" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>186</v>
+        <v>43</v>
       </c>
       <c r="I65" s="6">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J65" s="6">
         <v>10</v>
       </c>
       <c r="K65" s="6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="L65" s="9" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="M65" s="7">
-        <v>0.55000000000000004</v>
+        <v>0.75</v>
       </c>
       <c r="N65" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="17">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>185</v>
+        <v>23</v>
       </c>
       <c r="D66" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E66" s="18">
-        <v>54.308265929999997</v>
+        <v>55.420122130000003</v>
       </c>
       <c r="F66" s="18">
-        <v>24.661928849999999</v>
+        <v>25.10494164</v>
       </c>
       <c r="G66" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H66" s="12" t="s">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="I66" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J66" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K66" s="6">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="L66" s="9" t="s">
-        <v>188</v>
+        <v>25</v>
       </c>
       <c r="M66" s="7">
-        <v>0.69</v>
+        <v>0.76</v>
       </c>
       <c r="N66" s="7" t="s">
         <v>26</v>
@@ -4059,43 +4059,43 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="17">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="D67" s="5">
         <v>5</v>
       </c>
       <c r="E67" s="18">
-        <v>54.308265929999997</v>
+        <v>54.755648749999999</v>
       </c>
       <c r="F67" s="18">
-        <v>24.661928849999999</v>
+        <v>22.987372709999999</v>
       </c>
       <c r="G67" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>67</v>
+        <v>173</v>
       </c>
       <c r="I67" s="6">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J67" s="6">
         <v>10</v>
       </c>
       <c r="K67" s="6">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="L67" s="9" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="M67" s="7">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="N67" s="7" t="s">
         <v>26</v>
@@ -4103,383 +4103,383 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="17">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>190</v>
+        <v>103</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="D68" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E68" s="18">
-        <v>56.0705004</v>
+        <v>55.250778369999999</v>
       </c>
       <c r="F68" s="18">
-        <v>24.086051139999999</v>
+        <v>26.600762320000001</v>
       </c>
       <c r="G68" s="5" t="s">
-        <v>42</v>
+        <v>105</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>177</v>
+        <v>110</v>
       </c>
       <c r="I68" s="6">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="J68" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K68" s="6">
         <v>2016</v>
       </c>
       <c r="L68" s="9" t="s">
-        <v>191</v>
+        <v>111</v>
       </c>
       <c r="M68" s="7">
-        <v>0.45</v>
+        <v>0.78</v>
       </c>
       <c r="N68" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="17">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D69" s="5">
         <v>5</v>
       </c>
       <c r="E69" s="18">
-        <v>56.0705004</v>
+        <v>54.308265929999997</v>
       </c>
       <c r="F69" s="18">
-        <v>24.086051139999999</v>
+        <v>24.661928849999999</v>
       </c>
       <c r="G69" s="5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H69" s="12" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="I69" s="6">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="J69" s="6">
         <v>10</v>
       </c>
       <c r="K69" s="6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="L69" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="M69" s="7">
-        <v>0.49</v>
+        <v>0.78</v>
       </c>
       <c r="N69" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="17">
-        <v>26</v>
+        <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>190</v>
+        <v>63</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>180</v>
+        <v>64</v>
       </c>
       <c r="D70" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E70" s="18">
-        <v>56.0705004</v>
+        <v>54.353197020000003</v>
       </c>
       <c r="F70" s="18">
-        <v>24.086051139999999</v>
+        <v>24.83006962</v>
       </c>
       <c r="G70" s="5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H70" s="12" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="I70" s="6">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J70" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K70" s="6">
         <v>2022</v>
       </c>
       <c r="L70" s="9" t="s">
-        <v>193</v>
+        <v>68</v>
       </c>
       <c r="M70" s="7">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="N70" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="17">
-        <v>37</v>
+        <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>194</v>
+        <v>81</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>195</v>
+        <v>82</v>
       </c>
       <c r="D71" s="5">
+        <v>2</v>
+      </c>
+      <c r="E71" s="18">
+        <v>55.91262141</v>
+      </c>
+      <c r="F71" s="18">
+        <v>21.780353040000001</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="I71" s="6">
         <v>5</v>
-      </c>
-      <c r="E71" s="18">
-        <v>55.929042940000002</v>
-      </c>
-      <c r="F71" s="18">
-        <v>24.291695959999998</v>
-      </c>
-      <c r="G71" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H71" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="I71" s="6">
-        <v>1</v>
       </c>
       <c r="J71" s="6">
         <v>10</v>
       </c>
       <c r="K71" s="6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="L71" s="9" t="s">
-        <v>196</v>
+        <v>86</v>
       </c>
       <c r="M71" s="7">
-        <v>0.56999999999999995</v>
+        <v>0.79</v>
       </c>
       <c r="N71" s="7" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="17">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>194</v>
+        <v>32</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>195</v>
+        <v>33</v>
       </c>
       <c r="D72" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" s="18">
-        <v>55.929042940000002</v>
+        <v>54.755461689999997</v>
       </c>
       <c r="F72" s="18">
-        <v>24.291695959999998</v>
+        <v>24.957577279999999</v>
       </c>
       <c r="G72" s="5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H72" s="12" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="I72" s="6">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J72" s="6">
         <v>9</v>
       </c>
       <c r="K72" s="6">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="L72" s="9" t="s">
-        <v>197</v>
+        <v>39</v>
       </c>
       <c r="M72" s="7">
-        <v>0.67</v>
+        <v>0.81</v>
       </c>
       <c r="N72" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="17">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>194</v>
+        <v>96</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
       <c r="D73" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E73" s="18">
-        <v>55.929042940000002</v>
+        <v>55.080792750000001</v>
       </c>
       <c r="F73" s="18">
-        <v>24.291695959999998</v>
+        <v>22.743415259999999</v>
       </c>
       <c r="G73" s="5" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="H73" s="12" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="I73" s="6">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="J73" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K73" s="6">
         <v>2015</v>
       </c>
       <c r="L73" s="9" t="s">
-        <v>199</v>
+        <v>102</v>
       </c>
       <c r="M73" s="7">
-        <v>0.72</v>
+        <v>0.82</v>
       </c>
       <c r="N73" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="17">
-        <v>34</v>
+        <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="D74" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E74" s="18">
-        <v>55.621911740000002</v>
+        <v>54.201132620000003</v>
       </c>
       <c r="F74" s="18">
-        <v>25.5652358</v>
+        <v>24.371298920000001</v>
       </c>
       <c r="G74" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H74" s="12" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="I74" s="6">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J74" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K74" s="6">
         <v>2019</v>
       </c>
       <c r="L74" s="9" t="s">
-        <v>202</v>
+        <v>121</v>
       </c>
       <c r="M74" s="7">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="N74" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="17">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D75" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E75" s="18">
-        <v>55.621911740000002</v>
+        <v>56.124192209999997</v>
       </c>
       <c r="F75" s="18">
-        <v>25.5652358</v>
+        <v>21.263878009999999</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H75" s="12" t="s">
-        <v>203</v>
+        <v>56</v>
       </c>
       <c r="I75" s="6">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J75" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K75" s="6">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>204</v>
+        <v>57</v>
       </c>
       <c r="M75" s="7">
-        <v>0.59</v>
+        <v>0.83</v>
       </c>
       <c r="N75" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="17">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="D76" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E76" s="18">
-        <v>55.621911740000002</v>
+        <v>56.256980110000001</v>
       </c>
       <c r="F76" s="18">
-        <v>25.5652358</v>
+        <v>21.64241196</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="H76" s="12" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="I76" s="6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J76" s="6">
         <v>9</v>
@@ -4488,328 +4488,326 @@
         <v>2022</v>
       </c>
       <c r="L76" s="9" t="s">
-        <v>205</v>
+        <v>154</v>
       </c>
       <c r="M76" s="7">
-        <v>0.71</v>
+        <v>0.83</v>
       </c>
       <c r="N76" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="17">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>206</v>
+        <v>89</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>207</v>
+        <v>90</v>
       </c>
       <c r="D77" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E77" s="18">
-        <v>54.755648749999999</v>
+        <v>54.341399729999999</v>
       </c>
       <c r="F77" s="18">
-        <v>22.987372709999999</v>
+        <v>24.88637937</v>
       </c>
       <c r="G77" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>208</v>
+        <v>94</v>
       </c>
       <c r="I77" s="6">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="J77" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K77" s="6">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>209</v>
+        <v>95</v>
       </c>
       <c r="M77" s="7">
-        <v>0.56999999999999995</v>
+        <v>0.86</v>
       </c>
       <c r="N77" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="17">
+        <v>77</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>207</v>
-      </c>
       <c r="D78" s="5">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E78" s="18">
-        <v>54.755648749999999</v>
+        <v>54.353197020000003</v>
       </c>
       <c r="F78" s="18">
-        <v>22.987372709999999</v>
+        <v>24.83006962</v>
       </c>
       <c r="G78" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="I78" s="6">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J78" s="6">
         <v>10</v>
       </c>
       <c r="K78" s="6">
-        <v>2022</v>
+        <v>2016</v>
       </c>
       <c r="L78" s="9" t="s">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="M78" s="7">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="N78" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="17">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>206</v>
+        <v>81</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="D79" s="5">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E79" s="18">
-        <v>54.755648749999999</v>
+        <v>55.91262141</v>
       </c>
       <c r="F79" s="18">
-        <v>22.987372709999999</v>
+        <v>21.780353040000001</v>
       </c>
       <c r="G79" s="5" t="s">
         <v>16</v>
       </c>
       <c r="H79" s="12" t="s">
-        <v>173</v>
+        <v>87</v>
       </c>
       <c r="I79" s="6">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J79" s="6">
         <v>10</v>
       </c>
       <c r="K79" s="6">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="L79" s="9" t="s">
-        <v>211</v>
+        <v>88</v>
       </c>
       <c r="M79" s="7">
-        <v>0.77</v>
+        <v>0.92</v>
       </c>
       <c r="N79" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="17">
+        <v>79</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D80" s="5">
+        <v>3</v>
+      </c>
+      <c r="E80" s="18">
+        <v>54.201132620000003</v>
+      </c>
+      <c r="F80" s="18">
+        <v>24.371298920000001</v>
+      </c>
+      <c r="G80" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="I80" s="6">
+        <v>13</v>
+      </c>
+      <c r="J80" s="6">
         <v>10</v>
       </c>
-      <c r="B80" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D80" s="9">
-        <v>5</v>
-      </c>
-      <c r="E80" s="18">
-        <v>56.228900000000003</v>
-      </c>
-      <c r="F80" s="18">
-        <v>24.407499999999999</v>
-      </c>
-      <c r="G80" t="s">
-        <v>42</v>
-      </c>
-      <c r="H80" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="I80" s="9">
-        <v>21</v>
-      </c>
-      <c r="J80" s="9">
-        <v>9</v>
-      </c>
-      <c r="K80" s="9">
-        <v>2020</v>
+      <c r="K80" s="6">
+        <v>2015</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="M80" s="10">
-        <v>0.36</v>
-      </c>
-      <c r="N80" s="10" t="s">
-        <v>19</v>
+        <v>123</v>
+      </c>
+      <c r="M80" s="7">
+        <v>0.93</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="17">
-        <v>14</v>
-      </c>
-      <c r="B81" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D81" s="9">
-        <v>5</v>
+        <v>80</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" s="5">
+        <v>1</v>
       </c>
       <c r="E81" s="18">
-        <v>56.228900000000003</v>
+        <v>55.420122130000003</v>
       </c>
       <c r="F81" s="18">
-        <v>24.407499999999999</v>
-      </c>
-      <c r="G81" t="s">
-        <v>42</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>215</v>
-      </c>
-      <c r="I81" s="9">
-        <v>16</v>
-      </c>
-      <c r="J81" s="9">
-        <v>10</v>
-      </c>
-      <c r="K81" s="9">
-        <v>2017</v>
+        <v>25.10494164</v>
+      </c>
+      <c r="G81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I81" s="6">
+        <v>19</v>
+      </c>
+      <c r="J81" s="6">
+        <v>9</v>
+      </c>
+      <c r="K81" s="6">
+        <v>2022</v>
       </c>
       <c r="L81" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="M81" s="10">
-        <v>0.38</v>
-      </c>
-      <c r="N81" s="10" t="s">
-        <v>19</v>
+        <v>28</v>
+      </c>
+      <c r="M81" s="7">
+        <v>0.99</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="17">
+        <v>81</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B82" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C82" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D82" s="9">
-        <v>5</v>
+      <c r="D82" s="5">
+        <v>1</v>
       </c>
       <c r="E82" s="18">
-        <v>56.228900000000003</v>
+        <v>55.420122130000003</v>
       </c>
       <c r="F82" s="18">
-        <v>24.407499999999999</v>
-      </c>
-      <c r="G82" t="s">
-        <v>42</v>
-      </c>
-      <c r="H82" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="I82" s="9">
-        <v>26</v>
-      </c>
-      <c r="J82" s="9">
+        <v>25.10494164</v>
+      </c>
+      <c r="G82" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I82" s="6">
+        <v>20</v>
+      </c>
+      <c r="J82" s="6">
         <v>9</v>
       </c>
-      <c r="K82" s="9">
+      <c r="K82" s="6">
         <v>2016</v>
       </c>
       <c r="L82" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="M82" s="10">
-        <v>0.48</v>
-      </c>
-      <c r="N82" s="10" t="s">
-        <v>45</v>
+        <v>31</v>
+      </c>
+      <c r="M82" s="7">
+        <v>1</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="17">
-        <v>27</v>
-      </c>
-      <c r="B83" s="9" t="s">
-        <v>212</v>
-      </c>
-      <c r="C83" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D83" s="9">
-        <v>5</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D83" s="5">
+        <v>3</v>
       </c>
       <c r="E83" s="18">
-        <v>56.228900000000003</v>
+        <v>54.201132620000003</v>
       </c>
       <c r="F83" s="18">
-        <v>24.407499999999999</v>
-      </c>
-      <c r="G83" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="I83" s="16">
-        <v>28</v>
-      </c>
-      <c r="J83" s="16">
-        <v>9</v>
-      </c>
-      <c r="K83" s="9">
-        <v>2015</v>
+        <v>24.371298920000001</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H83" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="I83" s="6">
+        <v>17</v>
+      </c>
+      <c r="J83" s="6">
+        <v>10</v>
+      </c>
+      <c r="K83" s="6">
+        <v>2022</v>
       </c>
       <c r="L83" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="M83" s="10">
-        <v>0.5</v>
-      </c>
-      <c r="N83" s="10" t="s">
-        <v>45</v>
+        <v>125</v>
+      </c>
+      <c r="M83" s="7">
+        <v>1</v>
+      </c>
+      <c r="N83" s="7" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N83" xr:uid="{6161CF63-5B81-4EC6-87ED-9460C9AB9DAB}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:S83">
-    <sortCondition ref="D2:D83"/>
-    <sortCondition ref="B2:B83"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N83">
+    <sortCondition ref="A2:A83"/>
   </sortState>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
